--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,1537 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126189630</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>583062</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6969105</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126189633</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>583144</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6969210</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126189631</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>583138</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6969114</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126189629</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>583088</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6969020</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126189736</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>658</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>583149</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6969213</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126189592</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>583062</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6969091</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126189734</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>658</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>583068</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6969120</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126189666</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>583108</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6969122</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Över hela sälgstammen</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126189634</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>583099</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6969153</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126189737</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>583130</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6969164</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126189665</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80110</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>583100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6969120</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Liten bål på sälg,  ca 2x2cm</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126189632</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>583142</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6969146</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126189738</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91246</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>583130</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6969145</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126189630</v>
+        <v>126189633</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583062</v>
+        <v>583144</v>
       </c>
       <c r="R5" t="n">
-        <v>6969105</v>
+        <v>6969210</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126189633</v>
+        <v>126189630</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583144</v>
+        <v>583062</v>
       </c>
       <c r="R6" t="n">
-        <v>6969210</v>
+        <v>6969105</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,7 +1216,7 @@
         <v>126189631</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>126189629</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126189736</v>
+        <v>126189592</v>
       </c>
       <c r="B9" t="n">
-        <v>91528</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1478,9 +1478,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1489,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583149</v>
+        <v>583062</v>
       </c>
       <c r="R9" t="n">
-        <v>6969213</v>
+        <v>6969091</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1524,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1539,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126189592</v>
+        <v>126189736</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>91530</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1594,14 +1604,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1610,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583062</v>
+        <v>583149</v>
       </c>
       <c r="R10" t="n">
-        <v>6969091</v>
+        <v>6969213</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1645,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,12 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,7 +1690,7 @@
         <v>126189734</v>
       </c>
       <c r="B11" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>126189666</v>
       </c>
       <c r="B12" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>126189634</v>
       </c>
       <c r="B13" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126189737</v>
       </c>
       <c r="B14" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>126189665</v>
       </c>
       <c r="B15" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,42 +2280,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126189632</v>
+        <v>126189738</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>91248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583142</v>
+        <v>583130</v>
       </c>
       <c r="R16" t="n">
-        <v>6969146</v>
+        <v>6969145</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,42 +2396,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126189738</v>
+        <v>126189632</v>
       </c>
       <c r="B17" t="n">
-        <v>91246</v>
+        <v>98341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583130</v>
+        <v>583142</v>
       </c>
       <c r="R17" t="n">
-        <v>6969145</v>
+        <v>6969146</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -1445,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126189592</v>
+        <v>126189736</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>91530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1478,14 +1478,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1494,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583062</v>
+        <v>583149</v>
       </c>
       <c r="R9" t="n">
-        <v>6969091</v>
+        <v>6969213</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,12 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126189736</v>
+        <v>126189592</v>
       </c>
       <c r="B10" t="n">
-        <v>91530</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1604,9 +1594,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583149</v>
+        <v>583062</v>
       </c>
       <c r="R10" t="n">
-        <v>6969213</v>
+        <v>6969091</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1655,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>126189633</v>
       </c>
       <c r="B5" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>126189630</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>126189631</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>126189629</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126189736</v>
       </c>
       <c r="B9" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189734</v>
+        <v>126189666</v>
       </c>
       <c r="B11" t="n">
-        <v>91530</v>
+        <v>80076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,43 +1698,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583068</v>
+        <v>583108</v>
       </c>
       <c r="R11" t="n">
-        <v>6969120</v>
+        <v>6969122</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1778,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Över hela sälgstammen</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,6 +1792,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1803,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126189666</v>
+        <v>126189734</v>
       </c>
       <c r="B12" t="n">
-        <v>80076</v>
+        <v>91532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,45 +1822,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583108</v>
+        <v>583068</v>
       </c>
       <c r="R12" t="n">
-        <v>6969122</v>
+        <v>6969120</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1884,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,12 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Över hela sälgstammen</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,7 +1909,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>126189634</v>
       </c>
       <c r="B13" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126189737</v>
       </c>
       <c r="B14" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>126189738</v>
       </c>
       <c r="B16" t="n">
-        <v>91248</v>
+        <v>91250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>126189632</v>
       </c>
       <c r="B17" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189666</v>
+        <v>126189734</v>
       </c>
       <c r="B11" t="n">
-        <v>80076</v>
+        <v>91532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,45 +1698,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583108</v>
+        <v>583068</v>
       </c>
       <c r="R11" t="n">
-        <v>6969122</v>
+        <v>6969120</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1768,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,12 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Över hela sälgstammen</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,7 +1785,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1811,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126189734</v>
+        <v>126189666</v>
       </c>
       <c r="B12" t="n">
-        <v>91532</v>
+        <v>80076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,43 +1814,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583068</v>
+        <v>583108</v>
       </c>
       <c r="R12" t="n">
-        <v>6969120</v>
+        <v>6969122</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1890,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1894,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Över hela sälgstammen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,6 +1908,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>126189633</v>
       </c>
       <c r="B5" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>126189630</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>126189631</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>126189629</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126189736</v>
       </c>
       <c r="B9" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189734</v>
+        <v>126189666</v>
       </c>
       <c r="B11" t="n">
-        <v>91532</v>
+        <v>80076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,43 +1698,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583068</v>
+        <v>583108</v>
       </c>
       <c r="R11" t="n">
-        <v>6969120</v>
+        <v>6969122</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1778,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Över hela sälgstammen</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,6 +1792,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1803,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126189666</v>
+        <v>126189734</v>
       </c>
       <c r="B12" t="n">
-        <v>80076</v>
+        <v>91534</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,45 +1822,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583108</v>
+        <v>583068</v>
       </c>
       <c r="R12" t="n">
-        <v>6969122</v>
+        <v>6969120</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1884,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,12 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Över hela sälgstammen</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,7 +1909,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>126189634</v>
       </c>
       <c r="B13" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126189737</v>
       </c>
       <c r="B14" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>126189738</v>
       </c>
       <c r="B16" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>126189632</v>
       </c>
       <c r="B17" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>126189633</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>126189630</v>
       </c>
       <c r="B6" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>126189631</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>126189629</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126189736</v>
       </c>
       <c r="B9" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>126189592</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>126189666</v>
       </c>
       <c r="B11" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>126189734</v>
       </c>
       <c r="B12" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>126189634</v>
       </c>
       <c r="B13" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126189737</v>
       </c>
       <c r="B14" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>126189665</v>
       </c>
       <c r="B15" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,42 +2280,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126189738</v>
+        <v>126189632</v>
       </c>
       <c r="B16" t="n">
-        <v>91252</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583130</v>
+        <v>583142</v>
       </c>
       <c r="R16" t="n">
-        <v>6969145</v>
+        <v>6969146</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,42 +2396,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126189632</v>
+        <v>126189738</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>91256</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583142</v>
+        <v>583130</v>
       </c>
       <c r="R17" t="n">
-        <v>6969146</v>
+        <v>6969145</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189666</v>
+        <v>126189734</v>
       </c>
       <c r="B11" t="n">
-        <v>80080</v>
+        <v>91538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,45 +1698,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583108</v>
+        <v>583068</v>
       </c>
       <c r="R11" t="n">
-        <v>6969122</v>
+        <v>6969120</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1768,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,12 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Över hela sälgstammen</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,7 +1785,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1811,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126189734</v>
+        <v>126189666</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,43 +1814,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583068</v>
+        <v>583108</v>
       </c>
       <c r="R12" t="n">
-        <v>6969120</v>
+        <v>6969122</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1890,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1894,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Över hela sälgstammen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,6 +1908,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>126189633</v>
       </c>
       <c r="B5" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>126189630</v>
       </c>
       <c r="B6" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>126189631</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>126189629</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189734</v>
+        <v>126189666</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>80080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,43 +1698,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583068</v>
+        <v>583108</v>
       </c>
       <c r="R11" t="n">
-        <v>6969120</v>
+        <v>6969122</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1766,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1778,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Över hela sälgstammen</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,6 +1792,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1803,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126189666</v>
+        <v>126189734</v>
       </c>
       <c r="B12" t="n">
-        <v>80080</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,45 +1822,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583108</v>
+        <v>583068</v>
       </c>
       <c r="R12" t="n">
-        <v>6969122</v>
+        <v>6969120</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1884,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,12 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Över hela sälgstammen</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,7 +1909,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>126189634</v>
       </c>
       <c r="B13" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2280,42 +2280,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126189632</v>
+        <v>126189738</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>91256</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583142</v>
+        <v>583130</v>
       </c>
       <c r="R16" t="n">
-        <v>6969146</v>
+        <v>6969145</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,42 +2396,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126189738</v>
+        <v>126189632</v>
       </c>
       <c r="B17" t="n">
-        <v>91256</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583130</v>
+        <v>583142</v>
       </c>
       <c r="R17" t="n">
-        <v>6969145</v>
+        <v>6969146</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126189633</v>
+        <v>126189630</v>
       </c>
       <c r="B5" t="n">
         <v>98352</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583144</v>
+        <v>583062</v>
       </c>
       <c r="R5" t="n">
-        <v>6969210</v>
+        <v>6969105</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126189630</v>
+        <v>126189633</v>
       </c>
       <c r="B6" t="n">
         <v>98352</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583062</v>
+        <v>583144</v>
       </c>
       <c r="R6" t="n">
-        <v>6969105</v>
+        <v>6969210</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126189630</v>
+        <v>126189633</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583062</v>
+        <v>583144</v>
       </c>
       <c r="R5" t="n">
-        <v>6969105</v>
+        <v>6969210</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126189633</v>
+        <v>126189630</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583144</v>
+        <v>583062</v>
       </c>
       <c r="R6" t="n">
-        <v>6969210</v>
+        <v>6969105</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,7 +1216,7 @@
         <v>126189631</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>126189629</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126189736</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>126189592</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189666</v>
+        <v>126189734</v>
       </c>
       <c r="B11" t="n">
-        <v>80080</v>
+        <v>91541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,45 +1698,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583108</v>
+        <v>583068</v>
       </c>
       <c r="R11" t="n">
-        <v>6969122</v>
+        <v>6969120</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1768,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,12 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Över hela sälgstammen</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,7 +1785,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1811,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126189734</v>
+        <v>126189666</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>80083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,43 +1814,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583068</v>
+        <v>583108</v>
       </c>
       <c r="R12" t="n">
-        <v>6969120</v>
+        <v>6969122</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1890,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1894,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Över hela sälgstammen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,6 +1908,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>126189634</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126189737</v>
       </c>
       <c r="B14" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>126189665</v>
       </c>
       <c r="B15" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,42 +2280,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126189738</v>
+        <v>126189632</v>
       </c>
       <c r="B16" t="n">
-        <v>91256</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583130</v>
+        <v>583142</v>
       </c>
       <c r="R16" t="n">
-        <v>6969145</v>
+        <v>6969146</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,42 +2396,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126189632</v>
+        <v>126189738</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>91259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583142</v>
+        <v>583130</v>
       </c>
       <c r="R17" t="n">
-        <v>6969146</v>
+        <v>6969145</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2280,42 +2280,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126189632</v>
+        <v>126189738</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>91259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583142</v>
+        <v>583130</v>
       </c>
       <c r="R16" t="n">
-        <v>6969146</v>
+        <v>6969145</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,42 +2396,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126189738</v>
+        <v>126189632</v>
       </c>
       <c r="B17" t="n">
-        <v>91259</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583130</v>
+        <v>583142</v>
       </c>
       <c r="R17" t="n">
-        <v>6969145</v>
+        <v>6969146</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2280,42 +2280,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126189738</v>
+        <v>126189632</v>
       </c>
       <c r="B16" t="n">
-        <v>91259</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583130</v>
+        <v>583142</v>
       </c>
       <c r="R16" t="n">
-        <v>6969145</v>
+        <v>6969146</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,42 +2396,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126189632</v>
+        <v>126189738</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>91259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583142</v>
+        <v>583130</v>
       </c>
       <c r="R17" t="n">
-        <v>6969146</v>
+        <v>6969145</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3490,6 +3490,238 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133527176</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storfloåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>583067</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6969079</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133527171</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storfloåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>583084</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6969021</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2938,7 +2938,7 @@
         <v>583116</v>
       </c>
       <c r="R22" t="n">
-        <v>6969091</v>
+        <v>6969092</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2706,32 +2706,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133153663</v>
+        <v>133153601</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583117</v>
+        <v>583132</v>
       </c>
       <c r="R20" t="n">
-        <v>6969207</v>
+        <v>6969140</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,32 +2803,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133153601</v>
+        <v>133153663</v>
       </c>
       <c r="B21" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583132</v>
+        <v>583117</v>
       </c>
       <c r="R21" t="n">
-        <v>6969140</v>
+        <v>6969207</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2706,32 +2706,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133153601</v>
+        <v>133153663</v>
       </c>
       <c r="B20" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583132</v>
+        <v>583117</v>
       </c>
       <c r="R20" t="n">
-        <v>6969140</v>
+        <v>6969207</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,32 +2803,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133153663</v>
+        <v>133153601</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583117</v>
+        <v>583132</v>
       </c>
       <c r="R21" t="n">
-        <v>6969207</v>
+        <v>6969140</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2706,32 +2706,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133153663</v>
+        <v>133153601</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583117</v>
+        <v>583132</v>
       </c>
       <c r="R20" t="n">
-        <v>6969207</v>
+        <v>6969140</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,32 +2803,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133153601</v>
+        <v>133153663</v>
       </c>
       <c r="B21" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583132</v>
+        <v>583117</v>
       </c>
       <c r="R21" t="n">
-        <v>6969140</v>
+        <v>6969207</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,7 +2938,7 @@
         <v>583116</v>
       </c>
       <c r="R22" t="n">
-        <v>6969092</v>
+        <v>6969091</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2515,7 +2515,7 @@
         <v>133153665</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>133153520</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133153601</v>
+        <v>133153663</v>
       </c>
       <c r="B20" t="n">
-        <v>97995</v>
+        <v>79334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583132</v>
+        <v>583117</v>
       </c>
       <c r="R20" t="n">
-        <v>6969140</v>
+        <v>6969207</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,32 +2803,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133153663</v>
+        <v>133153601</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>97997</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583117</v>
+        <v>583132</v>
       </c>
       <c r="R21" t="n">
-        <v>6969207</v>
+        <v>6969140</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2903,7 @@
         <v>133153530</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>583116</v>
       </c>
       <c r="R22" t="n">
-        <v>6969091</v>
+        <v>6969092</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
         <v>133153606</v>
       </c>
       <c r="B24" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>133153673</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>133153672</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>133153648</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>133527171</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2612,7 +2612,7 @@
         <v>133153520</v>
       </c>
       <c r="B19" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133153663</v>
+        <v>133153601</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>98005</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583117</v>
+        <v>583132</v>
       </c>
       <c r="R20" t="n">
-        <v>6969207</v>
+        <v>6969140</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,32 +2803,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133153601</v>
+        <v>133153663</v>
       </c>
       <c r="B21" t="n">
-        <v>97997</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583132</v>
+        <v>583117</v>
       </c>
       <c r="R21" t="n">
-        <v>6969140</v>
+        <v>6969207</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2903,7 @@
         <v>133153530</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2997,55 +2997,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133153722</v>
+        <v>133153606</v>
       </c>
       <c r="B23" t="n">
-        <v>58119</v>
+        <v>98005</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583062</v>
+        <v>583111</v>
       </c>
       <c r="R23" t="n">
-        <v>6969028</v>
+        <v>6969117</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,12 +3062,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3104,45 +3094,55 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133153606</v>
+        <v>133153722</v>
       </c>
       <c r="B24" t="n">
-        <v>97997</v>
+        <v>58119</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583111</v>
+        <v>583062</v>
       </c>
       <c r="R24" t="n">
-        <v>6969117</v>
+        <v>6969028</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3398,7 +3398,7 @@
         <v>133153648</v>
       </c>
       <c r="B27" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>133527171</v>
       </c>
       <c r="B29" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2997,45 +2997,55 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133153606</v>
+        <v>133153722</v>
       </c>
       <c r="B23" t="n">
-        <v>98005</v>
+        <v>58119</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583111</v>
+        <v>583062</v>
       </c>
       <c r="R23" t="n">
-        <v>6969117</v>
+        <v>6969028</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,12 +3072,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3094,55 +3104,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133153722</v>
+        <v>133153606</v>
       </c>
       <c r="B24" t="n">
-        <v>58119</v>
+        <v>98005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583062</v>
+        <v>583111</v>
       </c>
       <c r="R24" t="n">
-        <v>6969028</v>
+        <v>6969117</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2997,55 +2997,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133153722</v>
+        <v>133153606</v>
       </c>
       <c r="B23" t="n">
-        <v>58119</v>
+        <v>98005</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583062</v>
+        <v>583111</v>
       </c>
       <c r="R23" t="n">
-        <v>6969028</v>
+        <v>6969117</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,12 +3062,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3104,45 +3094,55 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133153606</v>
+        <v>133153722</v>
       </c>
       <c r="B24" t="n">
-        <v>98005</v>
+        <v>58119</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583111</v>
+        <v>583062</v>
       </c>
       <c r="R24" t="n">
-        <v>6969117</v>
+        <v>6969028</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -2515,7 +2515,7 @@
         <v>133153665</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>133153520</v>
       </c>
       <c r="B19" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,32 +2706,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133153601</v>
+        <v>133153663</v>
       </c>
       <c r="B20" t="n">
-        <v>98005</v>
+        <v>79348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583132</v>
+        <v>583117</v>
       </c>
       <c r="R20" t="n">
-        <v>6969140</v>
+        <v>6969207</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,32 +2803,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133153663</v>
+        <v>133153601</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>98033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583117</v>
+        <v>583132</v>
       </c>
       <c r="R21" t="n">
-        <v>6969207</v>
+        <v>6969140</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2903,7 @@
         <v>133153530</v>
       </c>
       <c r="B22" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>583116</v>
       </c>
       <c r="R22" t="n">
-        <v>6969092</v>
+        <v>6969091</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
         <v>133153606</v>
       </c>
       <c r="B23" t="n">
-        <v>98005</v>
+        <v>98033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>133153722</v>
       </c>
       <c r="B24" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>133153673</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>133153672</v>
       </c>
       <c r="B26" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>133153648</v>
       </c>
       <c r="B27" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>133527176</v>
       </c>
       <c r="B28" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>133527171</v>
       </c>
       <c r="B29" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -3495,7 +3495,7 @@
         <v>133527176</v>
       </c>
       <c r="B28" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>133527171</v>
       </c>
       <c r="B29" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -3611,7 +3611,7 @@
         <v>133527171</v>
       </c>
       <c r="B29" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112538731</v>
+        <v>126189734</v>
       </c>
       <c r="B2" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källmyrberget, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583054</v>
+        <v>583068</v>
       </c>
       <c r="R2" t="n">
-        <v>6969081</v>
+        <v>6969120</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,65 +779,69 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112538732</v>
+        <v>126189736</v>
       </c>
       <c r="B3" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källmyrberget, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583056</v>
+        <v>583149</v>
       </c>
       <c r="R3" t="n">
-        <v>6969113</v>
+        <v>6969213</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +895,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,12 +910,7 @@
         <v>112538733</v>
       </c>
       <c r="B4" t="n">
-        <v>89661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,42 +1004,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126189633</v>
+        <v>126189737</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1025,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583144</v>
+        <v>583130</v>
       </c>
       <c r="R5" t="n">
-        <v>6969210</v>
+        <v>6969164</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1060,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1070,7 +1093,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,57 +1120,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126189630</v>
+        <v>133153530</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583062</v>
+        <v>583116</v>
       </c>
       <c r="R6" t="n">
-        <v>6969105</v>
+        <v>6969091</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,22 +1185,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,69 +1205,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126189631</v>
+        <v>133527171</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Storfloåsen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583138</v>
+        <v>583084</v>
       </c>
       <c r="R7" t="n">
-        <v>6969114</v>
+        <v>6969021</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,22 +1282,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>06:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,22 +1317,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126189629</v>
+        <v>126189738</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,31 +1344,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1373,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583088</v>
+        <v>583130</v>
       </c>
       <c r="R8" t="n">
-        <v>6969020</v>
+        <v>6969145</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1408,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1418,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,57 +1449,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126189736</v>
+        <v>133153555</v>
       </c>
       <c r="B9" t="n">
-        <v>91541</v>
+        <v>92188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>3008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583149</v>
+        <v>583116</v>
       </c>
       <c r="R9" t="n">
-        <v>6969213</v>
+        <v>6969091</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,22 +1514,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,74 +1534,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126189592</v>
+        <v>133153520</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583062</v>
+        <v>583128</v>
       </c>
       <c r="R10" t="n">
-        <v>6969091</v>
+        <v>6969139</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,27 +1611,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:56</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,69 +1631,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126189734</v>
+        <v>133153663</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583068</v>
+        <v>583117</v>
       </c>
       <c r="R11" t="n">
-        <v>6969120</v>
+        <v>6969207</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,22 +1708,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,71 +1728,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126189666</v>
+        <v>133153664</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583108</v>
+        <v>583088</v>
       </c>
       <c r="R12" t="n">
-        <v>6969122</v>
+        <v>6969188</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,27 +1805,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Över hela sälgstammen</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,29 +1819,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126189634</v>
+        <v>133153665</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,46 +1848,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583099</v>
+        <v>583143</v>
       </c>
       <c r="R13" t="n">
-        <v>6969153</v>
+        <v>6969223</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,22 +1902,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:14</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:14</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,69 +1922,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126189737</v>
+        <v>133153672</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583130</v>
+        <v>583109</v>
       </c>
       <c r="R14" t="n">
-        <v>6969164</v>
+        <v>6969199</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2117,22 +1999,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,39 +2019,39 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126189665</v>
+        <v>133153673</v>
       </c>
       <c r="B15" t="n">
-        <v>80118</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2187,29 +2059,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583100</v>
+        <v>583045</v>
       </c>
       <c r="R15" t="n">
-        <v>6969120</v>
+        <v>6969106</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2233,27 +2096,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Liten bål på sälg,  ca 2x2cm</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,22 +2116,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126189738</v>
+        <v>126189666</v>
       </c>
       <c r="B16" t="n">
-        <v>91259</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,43 +2139,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583130</v>
+        <v>583108</v>
       </c>
       <c r="R16" t="n">
-        <v>6969145</v>
+        <v>6969122</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2359,7 +2209,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2219,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Över hela sälgstammen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,6 +2233,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2396,42 +2252,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126189632</v>
+        <v>126189665</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>80467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2440,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583142</v>
+        <v>583100</v>
       </c>
       <c r="R17" t="n">
-        <v>6969146</v>
+        <v>6969120</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2475,7 +2331,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2341,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Liten bål på sälg,  ca 2x2cm</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,48 +2373,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133153665</v>
+        <v>133527176</v>
       </c>
       <c r="B18" t="n">
-        <v>79348</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Storfloåsen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583143</v>
+        <v>583067</v>
       </c>
       <c r="R18" t="n">
-        <v>6969223</v>
+        <v>6969079</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2577,12 +2438,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,60 +2473,78 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133153520</v>
+        <v>126189592</v>
       </c>
       <c r="B19" t="n">
-        <v>91910</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583128</v>
+        <v>583062</v>
       </c>
       <c r="R19" t="n">
-        <v>6969139</v>
+        <v>6969091</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2674,12 +2568,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,22 +2603,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133153663</v>
+        <v>133153968</v>
       </c>
       <c r="B20" t="n">
-        <v>79348</v>
+        <v>58519</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,34 +2626,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>102990</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583117</v>
+        <v>583048</v>
       </c>
       <c r="R20" t="n">
-        <v>6969207</v>
+        <v>6968985</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,12 +2690,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2722,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133153601</v>
+        <v>133153925</v>
       </c>
       <c r="B21" t="n">
-        <v>98033</v>
+        <v>58349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,34 +2733,44 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583132</v>
+        <v>583051</v>
       </c>
       <c r="R21" t="n">
-        <v>6969140</v>
+        <v>6968993</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2868,12 +2797,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133153530</v>
+        <v>133153722</v>
       </c>
       <c r="B22" t="n">
-        <v>91947</v>
+        <v>58136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,34 +2840,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583116</v>
+        <v>583062</v>
       </c>
       <c r="R22" t="n">
-        <v>6969091</v>
+        <v>6969028</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2965,12 +2904,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,45 +2936,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133153606</v>
+        <v>112538731</v>
       </c>
       <c r="B23" t="n">
-        <v>98033</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Källmyrberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583111</v>
+        <v>583053</v>
       </c>
       <c r="R23" t="n">
-        <v>6969117</v>
+        <v>6969081</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,12 +3001,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,67 +3021,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133153722</v>
+        <v>112538732</v>
       </c>
       <c r="B24" t="n">
-        <v>58126</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Källmyrberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583062</v>
+        <v>583056</v>
       </c>
       <c r="R24" t="n">
-        <v>6969028</v>
+        <v>6969113</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,12 +3098,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,60 +3118,69 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133153673</v>
+        <v>126189629</v>
       </c>
       <c r="B25" t="n">
-        <v>79348</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583045</v>
+        <v>583088</v>
       </c>
       <c r="R25" t="n">
-        <v>6969106</v>
+        <v>6969020</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3266,12 +3204,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3286,60 +3234,69 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133153672</v>
+        <v>126189630</v>
       </c>
       <c r="B26" t="n">
-        <v>79348</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583109</v>
+        <v>583062</v>
       </c>
       <c r="R26" t="n">
-        <v>6969199</v>
+        <v>6969105</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3363,12 +3320,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,22 +3350,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133153648</v>
+        <v>126189631</v>
       </c>
       <c r="B27" t="n">
-        <v>99168</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3423,20 +3390,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583086</v>
+        <v>583138</v>
       </c>
       <c r="R27" t="n">
-        <v>6969021</v>
+        <v>6969114</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3460,12 +3436,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3480,60 +3466,69 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133527176</v>
+        <v>126189632</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storfloåsen, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583067</v>
+        <v>583142</v>
       </c>
       <c r="R28" t="n">
-        <v>6969079</v>
+        <v>6969146</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3557,27 +3552,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>06:25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3592,64 +3582,69 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133527171</v>
+        <v>126189633</v>
       </c>
       <c r="B29" t="n">
-        <v>91960</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storfloåsen, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583084</v>
+        <v>583144</v>
       </c>
       <c r="R29" t="n">
-        <v>6969021</v>
+        <v>6969210</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3673,27 +3668,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>06:28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,19 +3698,422 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126189634</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>583099</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6969153</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133153648</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>583086</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6969021</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133153601</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>583132</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6969140</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133153606</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>583111</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6969117</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48783-2023 artfynd.xlsx
+++ b/artfynd/A 48783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189734</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189736</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538733</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189737</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153530</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133527171</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189738</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153555</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153520</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153663</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,6 +1889,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153664</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1931,6 +1991,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153665</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2028,6 +2093,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153672</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2125,6 +2195,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153673</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2249,6 +2324,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189666</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2370,6 +2450,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189665</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2486,6 +2571,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133527176</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2612,6 +2702,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189592</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2719,6 +2814,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153968</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2826,6 +2926,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153925</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2933,6 +3038,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153722</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3030,6 +3140,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538731</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3127,6 +3242,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538732</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3243,6 +3363,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189629</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3359,6 +3484,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189630</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3475,6 +3605,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189631</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3591,6 +3726,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189632</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3707,6 +3847,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189633</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3823,6 +3968,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189634</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3920,6 +4070,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153648</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4017,6 +4172,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153601</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4114,8 +4274,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153606</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>